--- a/content/downloads/sample-brief-and-evaluation-template.xlsx
+++ b/content/downloads/sample-brief-and-evaluation-template.xlsx
@@ -629,7 +629,7 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>Decides exporters and shipping options</t>
+          <t>Decides which coffees and shipping options fit</t>
         </is>
       </c>
     </row>
